--- a/Week 4 CellChat/data/Revenue Input.xlsx
+++ b/Week 4 CellChat/data/Revenue Input.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://keckmedicine-my.sharepoint.com/personal/j_nelson_med_usc_edu/Documents/Nelson USC Lab/JWN Effort Sankey Project/Dataset/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uscedu-my.sharepoint.com/personal/jnelson4_usc_edu/Documents/Github/score/Week 4 CellChat/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{D5FE7890-1A2F-4BDD-A803-A093EAE2A0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5008F51-7DF7-4A8A-8284-4DD71894E0F7}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{D5FE7890-1A2F-4BDD-A803-A093EAE2A0D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{719486E3-8DA9-4C32-866E-647E1CAA623B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1567F8CE-0A05-4DD2-90CE-F38A0CB6332F}"/>
   </bookViews>
@@ -451,6 +451,7 @@
     <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
